--- a/public/wfa_0-to-5-years_zscores.xlsx
+++ b/public/wfa_0-to-5-years_zscores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yry\Desktop\SKRIPSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC2BB3B-D9AC-4B40-A313-AF5ABBD40394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64942B6-E993-44D2-84D8-81B9AB994ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,12 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="15">
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
   <si>
     <t>month</t>
   </si>
@@ -65,6 +59,12 @@
   </si>
   <si>
     <t>sigma</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -551,9 +551,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -599,7 +602,10 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
@@ -621,11 +627,11 @@
   <autoFilter ref="A1:M123" xr:uid="{F872874E-142C-4E89-B30A-81BD572C36D7}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D5DCF007-391E-46A1-BB77-57A7FA57C2DC}" name="month"/>
-    <tableColumn id="2" xr3:uid="{B4D95983-DA48-40D0-89AC-6E7D8EFCB7EC}" name="gender"/>
+    <tableColumn id="2" xr3:uid="{B4D95983-DA48-40D0-89AC-6E7D8EFCB7EC}" name="gender" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{4A5BA6D4-7E2E-46ED-96D8-FF0E52B00A8B}" name="lambda"/>
     <tableColumn id="4" xr3:uid="{8F6A5E95-A92B-4447-9E13-83B0B5411593}" name="mean"/>
     <tableColumn id="5" xr3:uid="{6C6EB401-2C13-4944-A848-07F099F0B5C5}" name="sigma"/>
-    <tableColumn id="6" xr3:uid="{29BC0E78-198F-4087-9809-040BE398AC32}" name="sd" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{29BC0E78-198F-4087-9809-040BE398AC32}" name="sd" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{34DC7164-00F1-422F-B526-0FCE34B99F9A}" name="minus_3sd"/>
     <tableColumn id="8" xr3:uid="{2C56F063-24E3-42BE-8C40-1B65207899DB}" name="minus_2sd"/>
     <tableColumn id="9" xr3:uid="{08C35C22-E46B-420B-8487-CF2C2F110CA3}" name="minus_1sd"/>
@@ -953,51 +959,51 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0.38090000000000002</v>
@@ -1037,8 +1043,8 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0.1714</v>
@@ -1078,8 +1084,8 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C4">
         <v>9.6199999999999994E-2</v>
@@ -1119,8 +1125,8 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
         <v>4.02E-2</v>
@@ -1160,8 +1166,8 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C6">
         <v>-5.0000000000000001E-3</v>
@@ -1201,8 +1207,8 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>1</v>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C7">
         <v>-4.2999999999999997E-2</v>
@@ -1242,8 +1248,8 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>1</v>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C8">
         <v>-7.5600000000000001E-2</v>
@@ -1283,8 +1289,8 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>1</v>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
         <v>-0.10390000000000001</v>
@@ -1324,8 +1330,8 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>1</v>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C10">
         <v>-0.1288</v>
@@ -1365,8 +1371,8 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>1</v>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>-0.1507</v>
@@ -1406,8 +1412,8 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>1</v>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C12">
         <v>-0.17</v>
@@ -1447,8 +1453,8 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>1</v>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C13">
         <v>-0.18720000000000001</v>
@@ -1488,8 +1494,8 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>1</v>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C14">
         <v>-0.2024</v>
@@ -1529,8 +1535,8 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>1</v>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C15">
         <v>-0.21579999999999999</v>
@@ -1570,8 +1576,8 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>1</v>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C16">
         <v>-0.2278</v>
@@ -1611,8 +1617,8 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>1</v>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C17">
         <v>-0.2384</v>
@@ -1652,8 +1658,8 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>1</v>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C18">
         <v>-0.24779999999999999</v>
@@ -1693,8 +1699,8 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>1</v>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C19">
         <v>-0.25619999999999998</v>
@@ -1734,8 +1740,8 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>1</v>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C20">
         <v>-0.26369999999999999</v>
@@ -1775,8 +1781,8 @@
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>1</v>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C21">
         <v>-0.27029999999999998</v>
@@ -1816,8 +1822,8 @@
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>1</v>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C22">
         <v>-0.2762</v>
@@ -1857,8 +1863,8 @@
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>1</v>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C23">
         <v>-0.28149999999999997</v>
@@ -1898,8 +1904,8 @@
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>1</v>
+      <c r="B24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C24">
         <v>-0.28620000000000001</v>
@@ -1939,8 +1945,8 @@
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>1</v>
+      <c r="B25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C25">
         <v>-0.2903</v>
@@ -1980,8 +1986,8 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>1</v>
+      <c r="B26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C26">
         <v>-0.29409999999999997</v>
@@ -2021,8 +2027,8 @@
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>1</v>
+      <c r="B27" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C27">
         <v>-0.29749999999999999</v>
@@ -2062,8 +2068,8 @@
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>1</v>
+      <c r="B28" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C28">
         <v>-0.30049999999999999</v>
@@ -2103,8 +2109,8 @@
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>1</v>
+      <c r="B29" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C29">
         <v>-0.30320000000000003</v>
@@ -2144,8 +2150,8 @@
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>1</v>
+      <c r="B30" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C30">
         <v>-0.30570000000000003</v>
@@ -2185,8 +2191,8 @@
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>1</v>
+      <c r="B31" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C31">
         <v>-0.308</v>
@@ -2226,8 +2232,8 @@
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>1</v>
+      <c r="B32" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C32">
         <v>-0.31009999999999999</v>
@@ -2267,8 +2273,8 @@
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
-        <v>1</v>
+      <c r="B33" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C33">
         <v>-0.312</v>
@@ -2308,8 +2314,8 @@
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>1</v>
+      <c r="B34" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C34">
         <v>-0.31380000000000002</v>
@@ -2349,8 +2355,8 @@
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>1</v>
+      <c r="B35" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C35">
         <v>-0.3155</v>
@@ -2390,8 +2396,8 @@
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
-        <v>1</v>
+      <c r="B36" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C36">
         <v>-0.31709999999999999</v>
@@ -2431,8 +2437,8 @@
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
-        <v>1</v>
+      <c r="B37" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C37">
         <v>-0.31859999999999999</v>
@@ -2472,8 +2478,8 @@
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
-        <v>1</v>
+      <c r="B38" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C38">
         <v>-0.3201</v>
@@ -2513,8 +2519,8 @@
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
-        <v>1</v>
+      <c r="B39" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C39">
         <v>-0.3216</v>
@@ -2554,8 +2560,8 @@
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
-        <v>1</v>
+      <c r="B40" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C40">
         <v>-0.32300000000000001</v>
@@ -2595,8 +2601,8 @@
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
-        <v>1</v>
+      <c r="B41" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C41">
         <v>-0.32429999999999998</v>
@@ -2636,8 +2642,8 @@
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
-        <v>1</v>
+      <c r="B42" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C42">
         <v>-0.32569999999999999</v>
@@ -2677,8 +2683,8 @@
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
-        <v>1</v>
+      <c r="B43" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C43">
         <v>-0.32700000000000001</v>
@@ -2718,8 +2724,8 @@
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
-        <v>1</v>
+      <c r="B44" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C44">
         <v>-0.32829999999999998</v>
@@ -2759,8 +2765,8 @@
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
-        <v>1</v>
+      <c r="B45" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C45">
         <v>-0.3296</v>
@@ -2800,8 +2806,8 @@
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
-        <v>1</v>
+      <c r="B46" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C46">
         <v>-0.33090000000000003</v>
@@ -2841,8 +2847,8 @@
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
-        <v>1</v>
+      <c r="B47" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C47">
         <v>-0.3322</v>
@@ -2882,8 +2888,8 @@
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
-        <v>1</v>
+      <c r="B48" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C48">
         <v>-0.33350000000000002</v>
@@ -2923,8 +2929,8 @@
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
-        <v>1</v>
+      <c r="B49" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C49">
         <v>-0.33479999999999999</v>
@@ -2964,8 +2970,8 @@
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
-        <v>1</v>
+      <c r="B50" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C50">
         <v>-0.33610000000000001</v>
@@ -3005,8 +3011,8 @@
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
-        <v>1</v>
+      <c r="B51" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C51">
         <v>-0.33739999999999998</v>
@@ -3046,8 +3052,8 @@
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
-        <v>1</v>
+      <c r="B52" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C52">
         <v>-0.3387</v>
@@ -3087,8 +3093,8 @@
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="s">
-        <v>1</v>
+      <c r="B53" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C53">
         <v>-0.34</v>
@@ -3128,8 +3134,8 @@
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="s">
-        <v>1</v>
+      <c r="B54" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C54">
         <v>-0.34139999999999998</v>
@@ -3169,8 +3175,8 @@
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="s">
-        <v>1</v>
+      <c r="B55" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C55">
         <v>-0.3427</v>
@@ -3210,8 +3216,8 @@
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
-        <v>1</v>
+      <c r="B56" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C56">
         <v>-0.34399999999999997</v>
@@ -3251,8 +3257,8 @@
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="s">
-        <v>1</v>
+      <c r="B57" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C57">
         <v>-0.3453</v>
@@ -3292,8 +3298,8 @@
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="s">
-        <v>1</v>
+      <c r="B58" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C58">
         <v>-0.34660000000000002</v>
@@ -3333,8 +3339,8 @@
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
-        <v>1</v>
+      <c r="B59" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C59">
         <v>-0.34789999999999999</v>
@@ -3374,8 +3380,8 @@
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="s">
-        <v>1</v>
+      <c r="B60" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C60">
         <v>-0.34920000000000001</v>
@@ -3415,8 +3421,8 @@
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
-        <v>1</v>
+      <c r="B61" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C61">
         <v>-0.35049999999999998</v>
@@ -3456,8 +3462,8 @@
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="s">
-        <v>1</v>
+      <c r="B62" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C62">
         <v>-0.3518</v>
@@ -3497,8 +3503,8 @@
       <c r="A63">
         <v>0</v>
       </c>
-      <c r="B63" t="s">
-        <v>0</v>
+      <c r="B63" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C63">
         <v>0.34870000000000001</v>
@@ -3538,8 +3544,8 @@
       <c r="A64">
         <v>1</v>
       </c>
-      <c r="B64" t="s">
-        <v>0</v>
+      <c r="B64" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C64">
         <v>0.22969999999999999</v>
@@ -3579,8 +3585,8 @@
       <c r="A65">
         <v>2</v>
       </c>
-      <c r="B65" t="s">
-        <v>0</v>
+      <c r="B65" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C65">
         <v>0.19700000000000001</v>
@@ -3620,8 +3626,8 @@
       <c r="A66">
         <v>3</v>
       </c>
-      <c r="B66" t="s">
-        <v>0</v>
+      <c r="B66" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C66">
         <v>0.17380000000000001</v>
@@ -3661,8 +3667,8 @@
       <c r="A67">
         <v>4</v>
       </c>
-      <c r="B67" t="s">
-        <v>0</v>
+      <c r="B67" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C67">
         <v>0.15529999999999999</v>
@@ -3702,8 +3708,8 @@
       <c r="A68">
         <v>5</v>
       </c>
-      <c r="B68" t="s">
-        <v>0</v>
+      <c r="B68" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C68">
         <v>0.13950000000000001</v>
@@ -3743,8 +3749,8 @@
       <c r="A69">
         <v>6</v>
       </c>
-      <c r="B69" t="s">
-        <v>0</v>
+      <c r="B69" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C69">
         <v>0.12570000000000001</v>
@@ -3784,8 +3790,8 @@
       <c r="A70">
         <v>7</v>
       </c>
-      <c r="B70" t="s">
-        <v>0</v>
+      <c r="B70" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C70">
         <v>0.1134</v>
@@ -3825,8 +3831,8 @@
       <c r="A71">
         <v>8</v>
       </c>
-      <c r="B71" t="s">
-        <v>0</v>
+      <c r="B71" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C71">
         <v>0.1021</v>
@@ -3866,8 +3872,8 @@
       <c r="A72">
         <v>9</v>
       </c>
-      <c r="B72" t="s">
-        <v>0</v>
+      <c r="B72" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C72">
         <v>9.1700000000000004E-2</v>
@@ -3907,8 +3913,8 @@
       <c r="A73">
         <v>10</v>
       </c>
-      <c r="B73" t="s">
-        <v>0</v>
+      <c r="B73" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C73">
         <v>8.2000000000000003E-2</v>
@@ -3948,8 +3954,8 @@
       <c r="A74">
         <v>11</v>
       </c>
-      <c r="B74" t="s">
-        <v>0</v>
+      <c r="B74" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C74">
         <v>7.2999999999999995E-2</v>
@@ -3989,8 +3995,8 @@
       <c r="A75">
         <v>12</v>
       </c>
-      <c r="B75" t="s">
-        <v>0</v>
+      <c r="B75" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C75">
         <v>6.4399999999999999E-2</v>
@@ -4030,8 +4036,8 @@
       <c r="A76">
         <v>13</v>
       </c>
-      <c r="B76" t="s">
-        <v>0</v>
+      <c r="B76" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C76">
         <v>5.6300000000000003E-2</v>
@@ -4071,8 +4077,8 @@
       <c r="A77">
         <v>14</v>
       </c>
-      <c r="B77" t="s">
-        <v>0</v>
+      <c r="B77" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C77">
         <v>4.87E-2</v>
@@ -4112,8 +4118,8 @@
       <c r="A78">
         <v>15</v>
       </c>
-      <c r="B78" t="s">
-        <v>0</v>
+      <c r="B78" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C78">
         <v>4.1300000000000003E-2</v>
@@ -4153,8 +4159,8 @@
       <c r="A79">
         <v>16</v>
       </c>
-      <c r="B79" t="s">
-        <v>0</v>
+      <c r="B79" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C79">
         <v>3.4299999999999997E-2</v>
@@ -4194,8 +4200,8 @@
       <c r="A80">
         <v>17</v>
       </c>
-      <c r="B80" t="s">
-        <v>0</v>
+      <c r="B80" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C80">
         <v>2.75E-2</v>
@@ -4235,8 +4241,8 @@
       <c r="A81">
         <v>18</v>
       </c>
-      <c r="B81" t="s">
-        <v>0</v>
+      <c r="B81" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C81">
         <v>2.1100000000000001E-2</v>
@@ -4276,8 +4282,8 @@
       <c r="A82">
         <v>19</v>
       </c>
-      <c r="B82" t="s">
-        <v>0</v>
+      <c r="B82" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C82">
         <v>1.4800000000000001E-2</v>
@@ -4317,8 +4323,8 @@
       <c r="A83">
         <v>20</v>
       </c>
-      <c r="B83" t="s">
-        <v>0</v>
+      <c r="B83" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C83">
         <v>8.6999999999999994E-3</v>
@@ -4358,8 +4364,8 @@
       <c r="A84">
         <v>21</v>
       </c>
-      <c r="B84" t="s">
-        <v>0</v>
+      <c r="B84" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C84">
         <v>2.8999999999999998E-3</v>
@@ -4399,8 +4405,8 @@
       <c r="A85">
         <v>22</v>
       </c>
-      <c r="B85" t="s">
-        <v>0</v>
+      <c r="B85" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C85">
         <v>-2.8E-3</v>
@@ -4440,8 +4446,8 @@
       <c r="A86">
         <v>23</v>
       </c>
-      <c r="B86" t="s">
-        <v>0</v>
+      <c r="B86" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C86">
         <v>-8.3000000000000001E-3</v>
@@ -4481,8 +4487,8 @@
       <c r="A87">
         <v>24</v>
       </c>
-      <c r="B87" t="s">
-        <v>0</v>
+      <c r="B87" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C87">
         <v>-1.37E-2</v>
@@ -4522,8 +4528,8 @@
       <c r="A88">
         <v>25</v>
       </c>
-      <c r="B88" t="s">
-        <v>0</v>
+      <c r="B88" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C88">
         <v>-1.89E-2</v>
@@ -4563,8 +4569,8 @@
       <c r="A89">
         <v>26</v>
       </c>
-      <c r="B89" t="s">
-        <v>0</v>
+      <c r="B89" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C89">
         <v>-2.4E-2</v>
@@ -4604,8 +4610,8 @@
       <c r="A90">
         <v>27</v>
       </c>
-      <c r="B90" t="s">
-        <v>0</v>
+      <c r="B90" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C90">
         <v>-2.8899999999999999E-2</v>
@@ -4645,8 +4651,8 @@
       <c r="A91">
         <v>28</v>
       </c>
-      <c r="B91" t="s">
-        <v>0</v>
+      <c r="B91" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C91">
         <v>-3.3700000000000001E-2</v>
@@ -4686,8 +4692,8 @@
       <c r="A92">
         <v>29</v>
       </c>
-      <c r="B92" t="s">
-        <v>0</v>
+      <c r="B92" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C92">
         <v>-3.85E-2</v>
@@ -4727,8 +4733,8 @@
       <c r="A93">
         <v>30</v>
       </c>
-      <c r="B93" t="s">
-        <v>0</v>
+      <c r="B93" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C93">
         <v>-4.3099999999999999E-2</v>
@@ -4768,8 +4774,8 @@
       <c r="A94">
         <v>31</v>
       </c>
-      <c r="B94" t="s">
-        <v>0</v>
+      <c r="B94" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C94">
         <v>-4.7600000000000003E-2</v>
@@ -4809,8 +4815,8 @@
       <c r="A95">
         <v>32</v>
       </c>
-      <c r="B95" t="s">
-        <v>0</v>
+      <c r="B95" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C95">
         <v>-5.1999999999999998E-2</v>
@@ -4850,8 +4856,8 @@
       <c r="A96">
         <v>33</v>
       </c>
-      <c r="B96" t="s">
-        <v>0</v>
+      <c r="B96" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C96">
         <v>-5.6399999999999999E-2</v>
@@ -4891,8 +4897,8 @@
       <c r="A97">
         <v>34</v>
       </c>
-      <c r="B97" t="s">
-        <v>0</v>
+      <c r="B97" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C97">
         <v>-6.0600000000000001E-2</v>
@@ -4932,8 +4938,8 @@
       <c r="A98">
         <v>35</v>
       </c>
-      <c r="B98" t="s">
-        <v>0</v>
+      <c r="B98" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C98">
         <v>-6.4799999999999996E-2</v>
@@ -4973,8 +4979,8 @@
       <c r="A99">
         <v>36</v>
       </c>
-      <c r="B99" t="s">
-        <v>0</v>
+      <c r="B99" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C99">
         <v>-6.8900000000000003E-2</v>
@@ -5014,8 +5020,8 @@
       <c r="A100">
         <v>37</v>
       </c>
-      <c r="B100" t="s">
-        <v>0</v>
+      <c r="B100" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C100">
         <v>-7.2900000000000006E-2</v>
@@ -5055,8 +5061,8 @@
       <c r="A101">
         <v>38</v>
       </c>
-      <c r="B101" t="s">
-        <v>0</v>
+      <c r="B101" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C101">
         <v>-7.6899999999999996E-2</v>
@@ -5096,8 +5102,8 @@
       <c r="A102">
         <v>39</v>
       </c>
-      <c r="B102" t="s">
-        <v>0</v>
+      <c r="B102" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C102">
         <v>-8.0799999999999997E-2</v>
@@ -5137,8 +5143,8 @@
       <c r="A103">
         <v>40</v>
       </c>
-      <c r="B103" t="s">
-        <v>0</v>
+      <c r="B103" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C103">
         <v>-8.4599999999999995E-2</v>
@@ -5178,8 +5184,8 @@
       <c r="A104">
         <v>41</v>
       </c>
-      <c r="B104" t="s">
-        <v>0</v>
+      <c r="B104" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C104">
         <v>-8.8300000000000003E-2</v>
@@ -5219,8 +5225,8 @@
       <c r="A105">
         <v>42</v>
       </c>
-      <c r="B105" t="s">
-        <v>0</v>
+      <c r="B105" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C105">
         <v>-9.1999999999999998E-2</v>
@@ -5260,8 +5266,8 @@
       <c r="A106">
         <v>43</v>
       </c>
-      <c r="B106" t="s">
-        <v>0</v>
+      <c r="B106" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C106">
         <v>-9.5699999999999993E-2</v>
@@ -5301,8 +5307,8 @@
       <c r="A107">
         <v>44</v>
       </c>
-      <c r="B107" t="s">
-        <v>0</v>
+      <c r="B107" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C107">
         <v>-9.9299999999999999E-2</v>
@@ -5342,8 +5348,8 @@
       <c r="A108">
         <v>45</v>
       </c>
-      <c r="B108" t="s">
-        <v>0</v>
+      <c r="B108" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C108">
         <v>-0.1028</v>
@@ -5383,8 +5389,8 @@
       <c r="A109">
         <v>46</v>
       </c>
-      <c r="B109" t="s">
-        <v>0</v>
+      <c r="B109" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C109">
         <v>-0.10630000000000001</v>
@@ -5424,8 +5430,8 @@
       <c r="A110">
         <v>47</v>
       </c>
-      <c r="B110" t="s">
-        <v>0</v>
+      <c r="B110" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C110">
         <v>-0.10970000000000001</v>
@@ -5465,8 +5471,8 @@
       <c r="A111">
         <v>48</v>
       </c>
-      <c r="B111" t="s">
-        <v>0</v>
+      <c r="B111" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C111">
         <v>-0.11310000000000001</v>
@@ -5506,8 +5512,8 @@
       <c r="A112">
         <v>49</v>
       </c>
-      <c r="B112" t="s">
-        <v>0</v>
+      <c r="B112" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C112">
         <v>-0.11650000000000001</v>
@@ -5547,8 +5553,8 @@
       <c r="A113">
         <v>50</v>
       </c>
-      <c r="B113" t="s">
-        <v>0</v>
+      <c r="B113" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C113">
         <v>-0.1198</v>
@@ -5588,8 +5594,8 @@
       <c r="A114">
         <v>51</v>
       </c>
-      <c r="B114" t="s">
-        <v>0</v>
+      <c r="B114" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C114">
         <v>-0.123</v>
@@ -5629,8 +5635,8 @@
       <c r="A115">
         <v>52</v>
       </c>
-      <c r="B115" t="s">
-        <v>0</v>
+      <c r="B115" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C115">
         <v>-0.12620000000000001</v>
@@ -5670,8 +5676,8 @@
       <c r="A116">
         <v>53</v>
       </c>
-      <c r="B116" t="s">
-        <v>0</v>
+      <c r="B116" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C116">
         <v>-0.12939999999999999</v>
@@ -5711,8 +5717,8 @@
       <c r="A117">
         <v>54</v>
       </c>
-      <c r="B117" t="s">
-        <v>0</v>
+      <c r="B117" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C117">
         <v>-0.13250000000000001</v>
@@ -5752,8 +5758,8 @@
       <c r="A118">
         <v>55</v>
       </c>
-      <c r="B118" t="s">
-        <v>0</v>
+      <c r="B118" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C118">
         <v>-0.1356</v>
@@ -5793,8 +5799,8 @@
       <c r="A119">
         <v>56</v>
       </c>
-      <c r="B119" t="s">
-        <v>0</v>
+      <c r="B119" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C119">
         <v>-0.13869999999999999</v>
@@ -5834,8 +5840,8 @@
       <c r="A120">
         <v>57</v>
       </c>
-      <c r="B120" t="s">
-        <v>0</v>
+      <c r="B120" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C120">
         <v>-0.14169999999999999</v>
@@ -5875,8 +5881,8 @@
       <c r="A121">
         <v>58</v>
       </c>
-      <c r="B121" t="s">
-        <v>0</v>
+      <c r="B121" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C121">
         <v>-0.1447</v>
@@ -5916,8 +5922,8 @@
       <c r="A122">
         <v>59</v>
       </c>
-      <c r="B122" t="s">
-        <v>0</v>
+      <c r="B122" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C122">
         <v>-0.1477</v>
@@ -5957,8 +5963,8 @@
       <c r="A123">
         <v>60</v>
       </c>
-      <c r="B123" t="s">
-        <v>0</v>
+      <c r="B123" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C123">
         <v>-0.15060000000000001</v>
